--- a/data/trans_dic/P32E$casa_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32E$casa_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,05; 53,0</t>
+          <t>21,09; 55,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,66; 54,5</t>
+          <t>5,65; 50,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,11; 45,96</t>
+          <t>19,85; 47,97</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,63; 71,59</t>
+          <t>34,22; 73,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,16; 67,01</t>
+          <t>26,22; 67,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,2; 64,99</t>
+          <t>35,32; 63,75</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40,38; 84,97</t>
+          <t>42,0; 84,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,24; 79,28</t>
+          <t>36,19; 78,16</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,64; 68,88</t>
+          <t>39,54; 69,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 50,87</t>
+          <t>12,47; 54,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,54; 61,11</t>
+          <t>36,62; 62,14</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43,15; 60,5</t>
+          <t>43,35; 61,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,41; 47,6</t>
+          <t>22,22; 47,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,39; 54,11</t>
+          <t>40,02; 55,19</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7187; 18100</t>
+          <t>7202; 18881</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>612; 5892</t>
+          <t>610; 5491</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8590; 20663</t>
+          <t>8924; 21565</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10759; 22905</t>
+          <t>10949; 23666</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5866; 14472</t>
+          <t>5663; 14618</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19399; 34829</t>
+          <t>18929; 34166</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9671; 20349</t>
+          <t>10058; 20139</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11551; 22756</t>
+          <t>10388; 22434</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21414; 37210</t>
+          <t>21357; 37502</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1943; 8929</t>
+          <t>2189; 9561</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26153; 43740</t>
+          <t>26209; 44473</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>62190; 87186</t>
+          <t>62476; 87956</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11715; 26045</t>
+          <t>12155; 25764</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>78322; 107576</t>
+          <t>79562; 109730</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$casa_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32E$casa_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,09; 55,29</t>
+          <t>19,64; 53,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 50,79</t>
+          <t>5,84; 51,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,85; 47,97</t>
+          <t>19,88; 47,88</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>53,78%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,22; 73,97</t>
+          <t>40,75; 77,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,22; 67,69</t>
+          <t>23,25; 62,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,32; 63,75</t>
+          <t>39,62; 68,26</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,97%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42,0; 84,09</t>
+          <t>40,17; 81,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 100,0</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,19; 78,16</t>
+          <t>42,94; 77,94</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,55%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,54; 69,42</t>
+          <t>40,5; 70,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,47; 54,47</t>
+          <t>13,36; 53,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,62; 62,14</t>
+          <t>33,9; 60,87</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>48,65%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43,35; 61,03</t>
+          <t>44,88; 62,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,22; 47,09</t>
+          <t>24,41; 49,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,02; 55,19</t>
+          <t>41,18; 56,08</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>12749</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14722</t>
+          <t>15095</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7202; 18881</t>
+          <t>6870; 18769</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>610; 5491</t>
+          <t>648; 5765</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8924; 21565</t>
+          <t>9158; 22060</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17381</t>
+          <t>23563</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9758</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27140</t>
+          <t>34439</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10949; 23666</t>
+          <t>15831; 29967</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5663; 14618</t>
+          <t>5857; 15717</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18929; 34166</t>
+          <t>25371; 43712</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15726</t>
+          <t>18857</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>21820</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10058; 20139</t>
+          <t>12105; 24679</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>97; 4755</t>
+          <t>0; 6248</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10388; 22434</t>
+          <t>15623; 28357</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>29636</t>
+          <t>31917</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34666</t>
+          <t>38436</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21357; 37502</t>
+          <t>23292; 40553</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2189; 9561</t>
+          <t>2893; 11621</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26209; 44473</t>
+          <t>26839; 48186</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>75145</t>
+          <t>87085</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93737</t>
+          <t>109790</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>62476; 87956</t>
+          <t>72468; 100652</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12155; 25764</t>
+          <t>15670; 31963</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79562; 109730</t>
+          <t>92920; 126553</t>
         </is>
       </c>
     </row>
